--- a/results_scenario_2/tables/table_fmf_scenario_2.xlsx
+++ b/results_scenario_2/tables/table_fmf_scenario_2.xlsx
@@ -479,37 +479,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30431.2 ± 9.0</t>
+          <t>50726.2 ± 15.3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25298.8 ± 53.1</t>
+          <t>42223.8 ± 36.2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>128.8 ± 4.4</t>
+          <t>206.8 ± 5.9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.8 ± 1.0</t>
+          <t>19.8 ± 1.5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>57.6 ± 1.1</t>
+          <t>96.5 ± 3.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>33.8 ± 2.5</t>
+          <t>49.2 ± 2.5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.0 ± 0.4</t>
+          <t>3.0 ± 0.7</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -534,37 +534,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30840.0 ± 20.8</t>
+          <t>51394.8 ± 21.4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>25604.8 ± 62.7</t>
+          <t>42705.7 ± 39.5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>132.0 ± 4.9</t>
+          <t>211.9 ± 5.6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12.2 ± 0.9</t>
+          <t>20.4 ± 1.6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>58.8 ± 0.9</t>
+          <t>99.7 ± 3.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>35.0 ± 2.4</t>
+          <t>50.5 ± 2.7</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.4 ± 0.2</t>
+          <t>3.0 ± 0.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -589,37 +589,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31362.6 ± 30.4</t>
+          <t>52254.1 ± 30.7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>26000.4 ± 73.8</t>
+          <t>43375.1 ± 48.2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>132.2 ± 5.2</t>
+          <t>215.7 ± 5.8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11.8 ± 0.8</t>
+          <t>20.8 ± 1.7</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>59.2 ± 0.9</t>
+          <t>102.0 ± 3.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>35.0 ± 2.3</t>
+          <t>51.5 ± 2.6</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.6 ± 0.2</t>
+          <t>3.1 ± 0.7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -644,37 +644,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31870.6 ± 28.5</t>
+          <t>53104.9 ± 40.1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>26412.0 ± 75.4</t>
+          <t>44045.8 ± 56.8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>135.4 ± 6.5</t>
+          <t>220.8 ± 5.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12.4 ± 0.9</t>
+          <t>21.8 ± 1.7</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.2 ± 1.5</t>
+          <t>105.2 ± 3.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>35.6 ± 2.4</t>
+          <t>52.5 ± 2.5</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.6 ± 0.2</t>
+          <t>3.2 ± 0.7</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -699,37 +699,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>32414.6 ± 38.2</t>
+          <t>53976.8 ± 42.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>26843.8 ± 77.1</t>
+          <t>44741.1 ± 62.4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>136.2 ± 6.4</t>
+          <t>227.2 ± 5.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12.0 ± 1.0</t>
+          <t>22.8 ± 1.7</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>63.0 ± 1.5</t>
+          <t>109.2 ± 4.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>35.0 ± 2.4</t>
+          <t>53.8 ± 2.5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.6 ± 0.2</t>
+          <t>3.5 ± 0.7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -754,37 +754,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32962.2 ± 40.2</t>
+          <t>54884.5 ± 46.5</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>27236.0 ± 78.7</t>
+          <t>45384.7 ± 64.3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>138.4 ± 6.6</t>
+          <t>231.5 ± 5.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>12.2 ± 1.1</t>
+          <t>23.4 ± 2.1</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>64.2 ± 1.3</t>
+          <t>112.2 ± 4.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>35.8 ± 2.7</t>
+          <t>54.2 ± 2.4</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.8 ± 0.3</t>
+          <t>3.5 ± 0.6</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -809,37 +809,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>33520.2 ± 53.9</t>
+          <t>55825.0 ± 50.9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>27645.6 ± 93.7</t>
+          <t>46066.4 ± 69.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>139.8 ± 7.1</t>
+          <t>234.2 ± 5.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11.6 ± 1.0</t>
+          <t>23.8 ± 2.0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>65.6 ± 1.7</t>
+          <t>114.0 ± 4.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>36.2 ± 2.9</t>
+          <t>55.0 ± 2.4</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.0 ± 0.4</t>
+          <t>3.6 ± 0.5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -864,37 +864,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>34043.2 ± 52.4</t>
+          <t>56755.4 ± 53.3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>28013.6 ± 78.8</t>
+          <t>46733.3 ± 72.9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>141.0 ± 6.7</t>
+          <t>237.8 ± 5.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11.0 ± 0.9</t>
+          <t>24.4 ± 1.9</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>66.8 ± 1.9</t>
+          <t>116.8 ± 4.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>36.8 ± 2.4</t>
+          <t>55.5 ± 2.5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.0 ± 0.4</t>
+          <t>3.5 ± 0.5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -919,37 +919,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>34614.8 ± 64.3</t>
+          <t>57726.7 ± 64.7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>28433.8 ± 86.9</t>
+          <t>47438.4 ± 80.9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>141.8 ± 6.0</t>
+          <t>240.6 ± 6.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>12.0 ± 1.3</t>
+          <t>24.2 ± 2.0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>67.0 ± 1.6</t>
+          <t>119.4 ± 4.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>36.6 ± 2.7</t>
+          <t>55.9 ± 2.5</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.0 ± 0.4</t>
+          <t>3.6 ± 0.5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -974,37 +974,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>35186.4 ± 63.5</t>
+          <t>58681.5 ± 68.3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>28823.4 ± 84.8</t>
+          <t>48111.3 ± 87.8</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>141.8 ± 7.0</t>
+          <t>243.3 ± 6.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.6 ± 1.0</t>
+          <t>24.6 ± 1.9</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>67.6 ± 2.5</t>
+          <t>121.7 ± 5.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>36.4 ± 2.8</t>
+          <t>55.9 ± 2.7</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3.2 ± 0.5</t>
+          <t>3.6 ± 0.5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1029,37 +1029,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>35672.6 ± 72.0</t>
+          <t>59503.8 ± 69.6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>29170.4 ± 89.8</t>
+          <t>48653.8 ± 89.3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>143.8 ± 6.7</t>
+          <t>245.8 ± 6.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11.6 ± 0.9</t>
+          <t>25.1 ± 1.9</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>68.2 ± 2.5</t>
+          <t>123.4 ± 5.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>37.6 ± 2.5</t>
+          <t>56.5 ± 2.5</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.4 ± 0.5</t>
+          <t>3.5 ± 0.5</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1084,37 +1084,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>36130.2 ± 71.1</t>
+          <t>60265.1 ± 73.1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>29500.4 ± 94.4</t>
+          <t>49163.4 ± 88.2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>148.2 ± 6.2</t>
+          <t>248.1 ± 6.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>12.4 ± 0.7</t>
+          <t>25.1 ± 1.9</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>71.0 ± 2.3</t>
+          <t>125.3 ± 5.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>38.6 ± 2.7</t>
+          <t>57.0 ± 2.6</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.4 ± 0.5</t>
+          <t>3.6 ± 0.5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1139,32 +1139,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>36565.2 ± 78.7</t>
+          <t>61002.7 ± 80.8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>29774.2 ± 104.9</t>
+          <t>49645.4 ± 97.8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>150.4 ± 5.8</t>
+          <t>250.7 ± 6.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13.8 ± 0.6</t>
+          <t>25.0 ± 1.9</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>72.4 ± 1.9</t>
+          <t>127.2 ± 5.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>38.0 ± 2.5</t>
+          <t>58.1 ± 2.8</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1194,37 +1194,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>37023.2 ± 84.1</t>
+          <t>61748.1 ± 86.2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>30066.0 ± 104.4</t>
+          <t>50118.3 ± 99.9</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>154.0 ± 6.7</t>
+          <t>252.8 ± 6.6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>13.4 ± 0.6</t>
+          <t>25.0 ± 1.9</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>76.8 ± 2.4</t>
+          <t>129.2 ± 5.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>37.6 ± 2.7</t>
+          <t>58.3 ± 2.5</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3.4 ± 0.5</t>
+          <t>3.5 ± 0.5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1249,37 +1249,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>37471.4 ± 96.9</t>
+          <t>62492.3 ± 89.9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>30326.6 ± 107.2</t>
+          <t>50577.6 ± 101.5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>155.0 ± 6.5</t>
+          <t>257.6 ± 6.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13.8 ± 1.0</t>
+          <t>25.9 ± 2.1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>79.2 ± 2.3</t>
+          <t>132.1 ± 5.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>36.2 ± 2.5</t>
+          <t>58.9 ± 2.6</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.2 ± 0.6</t>
+          <t>3.9 ± 0.6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1304,37 +1304,37 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>37922.8 ± 105.7</t>
+          <t>63224.1 ± 89.1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>30612.6 ± 111.5</t>
+          <t>51024.0 ± 103.4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>157.2 ± 6.3</t>
+          <t>261.2 ± 6.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.2 ± 1.1</t>
+          <t>26.9 ± 2.2</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>80.4 ± 2.1</t>
+          <t>134.1 ± 6.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>37.0 ± 2.6</t>
+          <t>59.6 ± 2.6</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.0 ± 0.7</t>
+          <t>4.0 ± 0.6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1359,37 +1359,37 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>38354.8 ± 107.6</t>
+          <t>63991.2 ± 90.0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>30876.8 ± 114.0</t>
+          <t>51485.3 ± 102.7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>158.2 ± 5.9</t>
+          <t>262.4 ± 6.9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14.0 ± 1.3</t>
+          <t>26.8 ± 2.3</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>80.8 ± 2.4</t>
+          <t>134.9 ± 6.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>37.8 ± 2.4</t>
+          <t>60.2 ± 2.7</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>3.0 ± 0.6</t>
+          <t>4.0 ± 0.6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1414,37 +1414,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>38798.8 ± 125.1</t>
+          <t>64755.9 ± 94.4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>31126.2 ± 127.0</t>
+          <t>51949.8 ± 105.2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>159.0 ± 5.4</t>
+          <t>266.6 ± 6.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>14.8 ± 1.4</t>
+          <t>27.0 ± 2.4</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>81.0 ± 2.2</t>
+          <t>137.8 ± 6.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>37.2 ± 1.9</t>
+          <t>61.6 ± 2.4</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3.4 ± 0.7</t>
+          <t>4.0 ± 0.7</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1469,37 +1469,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>39246.2 ± 117.8</t>
+          <t>65511.5 ± 98.9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>31372.4 ± 122.3</t>
+          <t>52392.4 ± 109.1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>164.0 ± 6.2</t>
+          <t>269.5 ± 6.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16.8 ± 1.2</t>
+          <t>27.5 ± 2.4</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>82.4 ± 2.5</t>
+          <t>139.9 ± 5.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>38.8 ± 2.0</t>
+          <t>62.1 ± 2.4</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3.4 ± 0.7</t>
+          <t>4.0 ± 0.7</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1524,37 +1524,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>39694.4 ± 122.3</t>
+          <t>66278.1 ± 102.7</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>31610.6 ± 122.9</t>
+          <t>52841.9 ± 114.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>167.8 ± 6.3</t>
+          <t>272.4 ± 6.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>17.4 ± 1.4</t>
+          <t>27.7 ± 2.4</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>85.0 ± 2.5</t>
+          <t>141.0 ± 6.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>39.2 ± 2.0</t>
+          <t>63.8 ± 2.5</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.6 ± 0.7</t>
+          <t>4.2 ± 0.7</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1579,37 +1579,37 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>40157.8 ± 122.8</t>
+          <t>67019.0 ± 107.7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>31847.0 ± 128.8</t>
+          <t>53188.8 ± 115.3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>167.8 ± 5.6</t>
+          <t>274.3 ± 6.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16.8 ± 1.4</t>
+          <t>27.8 ± 2.4</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>85.0 ± 1.9</t>
+          <t>141.9 ± 5.8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>40.0 ± 2.1</t>
+          <t>64.7 ± 2.6</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.8 ± 0.7</t>
+          <t>4.2 ± 0.8</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1634,37 +1634,37 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>40578.8 ± 130.3</t>
+          <t>67751.6 ± 106.2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>32056.8 ± 133.1</t>
+          <t>53558.9 ± 115.8</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>170.2 ± 5.4</t>
+          <t>278.3 ± 7.8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>17.2 ± 1.2</t>
+          <t>28.3 ± 2.4</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>86.0 ± 2.0</t>
+          <t>144.9 ± 6.1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>40.6 ± 1.7</t>
+          <t>65.2 ± 2.6</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.2 ± 0.9</t>
+          <t>4.3 ± 0.8</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1689,37 +1689,37 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>41012.6 ± 125.6</t>
+          <t>68482.3 ± 115.5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>32281.6 ± 123.3</t>
+          <t>53938.6 ± 124.8</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>171.0 ± 5.1</t>
+          <t>280.8 ± 7.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>17.0 ± 1.1</t>
+          <t>28.2 ± 2.5</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>87.6 ± 1.7</t>
+          <t>147.2 ± 5.7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>39.8 ± 1.7</t>
+          <t>65.3 ± 2.5</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4.4 ± 0.9</t>
+          <t>4.5 ± 0.8</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1744,37 +1744,37 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>41459.8 ± 139.6</t>
+          <t>69169.2 ± 119.0</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>32517.4 ± 134.8</t>
+          <t>54277.7 ± 132.3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>170.8 ± 4.7</t>
+          <t>283.8 ± 7.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17.0 ± 0.9</t>
+          <t>28.4 ± 2.5</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>88.2 ± 2.0</t>
+          <t>148.9 ± 5.5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>39.0 ± 1.7</t>
+          <t>66.2 ± 2.6</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4.4 ± 0.9</t>
+          <t>4.7 ± 0.8</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1799,37 +1799,37 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>41885.2 ± 148.2</t>
+          <t>69874.6 ± 124.4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>32748.8 ± 138.6</t>
+          <t>54637.7 ± 135.9</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>173.4 ± 5.1</t>
+          <t>286.1 ± 7.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>17.6 ± 0.9</t>
+          <t>28.3 ± 2.5</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>89.0 ± 1.5</t>
+          <t>150.8 ± 5.4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>40.2 ± 2.0</t>
+          <t>66.8 ± 2.8</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4.6 ± 1.0</t>
+          <t>4.7 ± 0.8</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1854,37 +1854,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>42331.8 ± 139.5</t>
+          <t>70576.8 ± 127.9</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>32995.0 ± 128.1</t>
+          <t>55002.8 ± 138.0</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>174.8 ± 4.9</t>
+          <t>290.4 ± 7.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>17.6 ± 1.1</t>
+          <t>29.0 ± 2.4</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>89.6 ± 1.4</t>
+          <t>152.5 ± 5.2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>40.8 ± 1.9</t>
+          <t>68.8 ± 3.0</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5.0 ± 0.9</t>
+          <t>4.8 ± 0.8</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1909,37 +1909,37 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>42748.6 ± 139.5</t>
+          <t>71275.1 ± 134.1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>33214.2 ± 139.5</t>
+          <t>55373.6 ± 136.4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>175.8 ± 4.0</t>
+          <t>292.6 ± 7.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>17.8 ± 1.1</t>
+          <t>28.9 ± 2.6</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>90.8 ± 1.1</t>
+          <t>154.3 ± 5.1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>40.4 ± 1.6</t>
+          <t>69.4 ± 3.0</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5.0 ± 0.9</t>
+          <t>4.5 ± 0.8</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1964,37 +1964,37 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>43183.0 ± 152.2</t>
+          <t>71966.6 ± 144.4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>33441.8 ± 148.4</t>
+          <t>55752.5 ± 142.5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>177.4 ± 3.2</t>
+          <t>296.1 ± 7.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17.6 ± 1.1</t>
+          <t>29.4 ± 2.7</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>91.4 ± 1.5</t>
+          <t>155.4 ± 5.2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>42.0 ± 1.4</t>
+          <t>71.0 ± 2.8</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.8 ± 0.9</t>
+          <t>4.8 ± 0.8</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2019,37 +2019,37 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>43581.0 ± 153.0</t>
+          <t>72620.2 ± 152.3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>33648.4 ± 144.6</t>
+          <t>56104.4 ± 148.1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>177.2 ± 2.8</t>
+          <t>299.7 ± 7.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>18.4 ± 1.2</t>
+          <t>29.8 ± 2.5</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>90.6 ± 1.8</t>
+          <t>157.8 ± 5.1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>42.2 ± 1.1</t>
+          <t>72.0 ± 2.9</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4.6 ± 0.9</t>
+          <t>5.0 ± 0.7</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2074,37 +2074,37 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>43974.4 ± 149.0</t>
+          <t>73263.6 ± 154.3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>33855.0 ± 147.3</t>
+          <t>56455.5 ± 149.5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>176.2 ± 3.5</t>
+          <t>301.2 ± 6.6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>18.6 ± 1.1</t>
+          <t>29.8 ± 2.6</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>90.4 ± 1.8</t>
+          <t>159.2 ± 5.2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>41.2 ± 1.4</t>
+          <t>72.2 ± 2.7</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4.6 ± 0.9</t>
+          <t>5.0 ± 0.8</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2129,37 +2129,37 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>44348.6 ± 152.0</t>
+          <t>73899.0 ± 159.2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>34068.6 ± 143.7</t>
+          <t>56809.8 ± 146.4</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>176.4 ± 3.3</t>
+          <t>303.6 ± 7.0</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18.2 ± 1.2</t>
+          <t>30.0 ± 2.8</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>91.8 ± 2.2</t>
+          <t>161.2 ± 5.3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>41.0 ± 1.2</t>
+          <t>72.4 ± 2.8</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4.4 ± 1.0</t>
+          <t>5.0 ± 0.8</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2184,37 +2184,37 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>44726.0 ± 151.0</t>
+          <t>74505.2 ± 166.1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>34306.2 ± 147.7</t>
+          <t>57182.7 ± 153.3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>176.2 ± 2.7</t>
+          <t>305.6 ± 6.8</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>18.0 ± 1.1</t>
+          <t>30.4 ± 2.8</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>92.4 ± 1.0</t>
+          <t>162.8 ± 5.2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>41.0 ± 1.1</t>
+          <t>72.5 ± 2.8</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>3.8 ± 1.0</t>
+          <t>5.0 ± 0.8</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2239,37 +2239,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>45069.8 ± 153.0</t>
+          <t>75151.1 ± 168.4</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>34522.6 ± 149.4</t>
+          <t>57584.2 ± 156.7</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>177.8 ± 3.0</t>
+          <t>307.1 ± 7.6</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19.0 ± 1.1</t>
+          <t>31.2 ± 2.6</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>93.4 ± 0.7</t>
+          <t>166.1 ± 5.7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>41.6 ± 1.3</t>
+          <t>73.4 ± 2.7</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4.0 ± 1.0</t>
+          <t>5.2 ± 0.8</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2294,37 +2294,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>45479.0 ± 164.7</t>
+          <t>75820.4 ± 177.8</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>34786.8 ± 149.1</t>
+          <t>58008.8 ± 160.9</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>178.2 ± 3.2</t>
+          <t>309.5 ± 7.8</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>18.6 ± 1.1</t>
+          <t>31.9 ± 2.6</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>95.0 ± 1.0</t>
+          <t>169.1 ± 6.0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>42.4 ± 1.2</t>
+          <t>74.5 ± 2.7</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4.0 ± 1.0</t>
+          <t>5.2 ± 0.8</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2349,37 +2349,37 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>45898.6 ± 153.7</t>
+          <t>76499.3 ± 178.9</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>35061.2 ± 141.5</t>
+          <t>58474.2 ± 161.2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>177.4 ± 2.8</t>
+          <t>311.2 ± 8.1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>18.4 ± 1.2</t>
+          <t>32.6 ± 2.6</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>95.8 ± 1.2</t>
+          <t>172.0 ± 6.0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>42.2 ± 0.9</t>
+          <t>75.5 ± 2.7</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4.2 ± 0.9</t>
+          <t>5.2 ± 0.8</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2404,37 +2404,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>46334.0 ± 173.8</t>
+          <t>77215.9 ± 183.7</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>35293.6 ± 158.3</t>
+          <t>58894.2 ± 167.5</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>177.2 ± 2.8</t>
+          <t>313.6 ± 7.7</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19.0 ± 1.2</t>
+          <t>33.3 ± 2.3</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>97.4 ± 1.9</t>
+          <t>175.4 ± 5.7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>42.4 ± 0.7</t>
+          <t>76.4 ± 2.7</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.2 ± 0.9</t>
+          <t>5.5 ± 0.8</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2459,37 +2459,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>46753.0 ± 187.0</t>
+          <t>77897.8 ± 187.1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>35553.6 ± 163.1</t>
+          <t>59323.3 ± 169.3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>178.0 ± 2.2</t>
+          <t>315.1 ± 8.0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19.4 ± 1.3</t>
+          <t>33.8 ± 2.1</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>99.4 ± 2.3</t>
+          <t>177.9 ± 6.0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>42.6 ± 0.4</t>
+          <t>77.1 ± 3.0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4.2 ± 0.9</t>
+          <t>5.5 ± 0.8</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2514,37 +2514,37 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>47153.6 ± 195.2</t>
+          <t>78584.0 ± 192.5</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>35805.6 ± 170.6</t>
+          <t>59769.6 ± 173.6</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>179.2 ± 2.9</t>
+          <t>317.2 ± 7.8</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>20.2 ± 1.4</t>
+          <t>33.9 ± 2.1</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>100.8 ± 2.7</t>
+          <t>181.1 ± 5.8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>43.2 ± 0.5</t>
+          <t>77.8 ± 3.2</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4.4 ± 0.9</t>
+          <t>5.5 ± 0.9</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2569,37 +2569,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>47246.8 ± 200.2</t>
+          <t>78741.6 ± 202.2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>35991.8 ± 168.9</t>
+          <t>60048.3 ± 180.6</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>180.2 ± 2.7</t>
+          <t>316.3 ± 7.5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20.6 ± 1.6</t>
+          <t>34.2 ± 2.1</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>102.8 ± 2.5</t>
+          <t>182.6 ± 5.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>43.4 ± 0.4</t>
+          <t>77.8 ± 3.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4.4 ± 0.9</t>
+          <t>5.5 ± 0.9</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2624,37 +2624,37 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>47665.6 ± 211.3</t>
+          <t>79456.1 ± 202.8</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>36267.4 ± 180.5</t>
+          <t>60504.4 ± 185.2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>182.8 ± 3.5</t>
+          <t>315.7 ± 7.6</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>21.8 ± 1.5</t>
+          <t>34.4 ± 2.2</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>104.8 ± 3.5</t>
+          <t>184.0 ± 5.7</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>44.2 ± 0.7</t>
+          <t>78.8 ± 2.9</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4.4 ± 0.9</t>
+          <t>5.5 ± 0.9</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2679,37 +2679,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>48074.6 ± 210.8</t>
+          <t>80149.2 ± 205.1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>36484.2 ± 187.2</t>
+          <t>60870.9 ± 193.9</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>183.6 ± 3.7</t>
+          <t>316.1 ± 8.0</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>22.4 ± 1.6</t>
+          <t>34.3 ± 2.3</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>105.6 ± 3.8</t>
+          <t>185.2 ± 5.6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>45.2 ± 1.0</t>
+          <t>80.0 ± 3.1</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4.2 ± 0.8</t>
+          <t>5.6 ± 0.9</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2734,37 +2734,37 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>48427.4 ± 219.2</t>
+          <t>80760.3 ± 201.0</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>36659.2 ± 198.6</t>
+          <t>61179.8 ± 192.4</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>184.2 ± 4.4</t>
+          <t>317.4 ± 7.7</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>22.8 ± 1.8</t>
+          <t>35.2 ± 2.4</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>106.2 ± 3.6</t>
+          <t>187.1 ± 5.6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>46.0 ± 1.2</t>
+          <t>80.5 ± 2.9</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4.2 ± 0.5</t>
+          <t>5.8 ± 0.8</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2789,37 +2789,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>48751.0 ± 217.0</t>
+          <t>81288.1 ± 201.3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>36814.6 ± 192.2</t>
+          <t>61434.2 ± 196.5</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>185.6 ± 4.3</t>
+          <t>316.3 ± 7.6</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>22.6 ± 1.8</t>
+          <t>35.5 ± 2.4</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>108.2 ± 3.6</t>
+          <t>187.9 ± 5.9</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>46.6 ± 1.4</t>
+          <t>80.8 ± 2.8</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4.4 ± 0.7</t>
+          <t>5.9 ± 0.9</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2844,37 +2844,37 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>48979.4 ± 210.2</t>
+          <t>81693.9 ± 211.5</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>36880.6 ± 193.1</t>
+          <t>61577.9 ± 201.5</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>185.4 ± 3.6</t>
+          <t>317.2 ± 7.6</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>22.4 ± 1.8</t>
+          <t>35.4 ± 2.6</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>109.6 ± 3.3</t>
+          <t>189.6 ± 5.8</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>46.4 ± 1.2</t>
+          <t>82.0 ± 2.7</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>4.4 ± 0.7</t>
+          <t>5.8 ± 0.9</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2899,37 +2899,37 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>49164.8 ± 209.3</t>
+          <t>82000.7 ± 220.9</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>36911.8 ± 193.2</t>
+          <t>61627.3 ± 207.7</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>184.0 ± 4.1</t>
+          <t>320.4 ± 7.2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>22.2 ± 1.9</t>
+          <t>36.6 ± 2.5</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>109.6 ± 3.5</t>
+          <t>191.7 ± 5.7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>45.8 ± 1.5</t>
+          <t>82.9 ± 3.0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>4.4 ± 0.7</t>
+          <t>5.9 ± 0.8</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2954,37 +2954,37 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>49341.4 ± 224.7</t>
+          <t>82278.5 ± 226.6</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>36839.8 ± 196.5</t>
+          <t>61467.2 ± 211.8</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>180.8 ± 3.8</t>
+          <t>318.9 ± 7.0</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>21.4 ± 1.7</t>
+          <t>36.4 ± 2.4</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>108.2 ± 3.1</t>
+          <t>191.8 ± 5.9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>45.4 ± 1.5</t>
+          <t>82.8 ± 2.9</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4.6 ± 0.8</t>
+          <t>5.9 ± 0.9</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3009,37 +3009,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>49479.0 ± 218.8</t>
+          <t>82513.6 ± 226.7</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>36728.0 ± 200.1</t>
+          <t>61319.9 ± 210.4</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>179.6 ± 3.8</t>
+          <t>317.5 ± 7.2</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>22.0 ± 1.6</t>
+          <t>36.5 ± 2.4</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>108.2 ± 3.8</t>
+          <t>191.2 ± 6.1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>44.4 ± 1.4</t>
+          <t>83.0 ± 2.8</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4.4 ± 0.7</t>
+          <t>5.8 ± 0.8</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3064,37 +3064,37 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>49576.0 ± 232.5</t>
+          <t>82664.9 ± 234.9</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>36589.4 ± 206.2</t>
+          <t>61092.3 ± 215.5</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>178.6 ± 3.1</t>
+          <t>316.1 ± 7.8</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>22.6 ± 1.9</t>
+          <t>36.5 ± 2.5</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>106.0 ± 3.8</t>
+          <t>190.6 ± 6.3</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>45.0 ± 1.9</t>
+          <t>82.8 ± 3.1</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4.6 ± 0.7</t>
+          <t>6.0 ± 0.8</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3119,37 +3119,37 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>49640.6 ± 234.6</t>
+          <t>82760.3 ± 239.6</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>36429.2 ± 207.8</t>
+          <t>60802.8 ± 220.2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>179.4 ± 3.3</t>
+          <t>314.8 ± 7.9</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>22.0 ± 1.8</t>
+          <t>36.0 ± 2.5</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>106.8 ± 3.3</t>
+          <t>189.7 ± 6.2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>45.8 ± 1.7</t>
+          <t>83.1 ± 3.1</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.8 ± 0.7</t>
+          <t>6.0 ± 0.8</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3174,37 +3174,37 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>49613.4 ± 236.0</t>
+          <t>82690.0 ± 240.5</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>36196.2 ± 209.6</t>
+          <t>60379.8 ± 221.8</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>179.2 ± 3.3</t>
+          <t>313.0 ± 7.7</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>21.2 ± 1.9</t>
+          <t>35.2 ± 2.6</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>106.4 ± 3.6</t>
+          <t>188.7 ± 6.1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>46.6 ± 1.1</t>
+          <t>82.8 ± 3.2</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>5.0 ± 0.9</t>
+          <t>6.2 ± 0.8</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3229,37 +3229,37 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>49523.0 ± 241.5</t>
+          <t>82543.2 ± 237.5</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>35895.4 ± 214.1</t>
+          <t>59877.6 ± 214.1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>180.4 ± 3.8</t>
+          <t>314.1 ± 7.4</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>21.2 ± 1.8</t>
+          <t>35.4 ± 2.5</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>107.8 ± 3.3</t>
+          <t>188.6 ± 5.7</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>46.4 ± 0.9</t>
+          <t>83.9 ± 3.3</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>5.0 ± 0.9</t>
+          <t>6.2 ± 0.9</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3284,37 +3284,37 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>49403.4 ± 242.8</t>
+          <t>82369.8 ± 239.3</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>35590.0 ± 217.2</t>
+          <t>59386.9 ± 210.8</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>181.8 ± 4.5</t>
+          <t>314.1 ± 7.5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>21.0 ± 1.7</t>
+          <t>35.5 ± 2.4</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>108.2 ± 3.2</t>
+          <t>189.2 ± 5.2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>47.6 ± 1.1</t>
+          <t>83.3 ± 3.7</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>5.0 ± 0.9</t>
+          <t>6.0 ± 0.8</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3339,37 +3339,37 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>49252.6 ± 232.1</t>
+          <t>82142.2 ± 237.1</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>35180.4 ± 208.3</t>
+          <t>58729.0 ± 207.1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>181.8 ± 5.0</t>
+          <t>312.4 ± 7.3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>22.2 ± 1.4</t>
+          <t>35.2 ± 2.4</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>107.6 ± 3.2</t>
+          <t>188.2 ± 5.2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>47.4 ± 1.9</t>
+          <t>82.7 ± 3.6</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4.6 ± 0.9</t>
+          <t>6.3 ± 0.9</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3394,37 +3394,37 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>49122.4 ± 237.6</t>
+          <t>81954.8 ± 239.4</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>34820.0 ± 208.3</t>
+          <t>58134.2 ± 206.8</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>180.4 ± 4.7</t>
+          <t>310.6 ± 7.5</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>22.0 ± 1.6</t>
+          <t>35.2 ± 2.5</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>106.8 ± 3.0</t>
+          <t>186.7 ± 5.6</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>46.8 ± 1.7</t>
+          <t>82.2 ± 3.6</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4.8 ± 1.0</t>
+          <t>6.5 ± 0.9</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3449,37 +3449,37 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>49030.2 ± 248.0</t>
+          <t>81814.1 ± 244.3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>34465.4 ± 207.9</t>
+          <t>57593.6 ± 204.7</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>180.0 ± 6.0</t>
+          <t>309.3 ± 7.3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>21.6 ± 1.5</t>
+          <t>34.5 ± 2.7</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>107.2 ± 3.8</t>
+          <t>185.6 ± 5.6</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>46.6 ± 1.6</t>
+          <t>82.7 ± 3.6</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4.6 ± 0.9</t>
+          <t>6.5 ± 0.9</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3504,37 +3504,37 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>48903.4 ± 246.5</t>
+          <t>81614.6 ± 245.6</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>34118.4 ± 201.9</t>
+          <t>56974.9 ± 207.9</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>179.8 ± 6.5</t>
+          <t>308.1 ± 7.9</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>22.2 ± 1.6</t>
+          <t>34.2 ± 2.8</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>106.2 ± 4.5</t>
+          <t>184.2 ± 5.9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>47.0 ± 2.1</t>
+          <t>83.2 ± 3.8</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>4.4 ± 0.9</t>
+          <t>6.3 ± 0.9</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3559,37 +3559,37 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>48736.4 ± 248.7</t>
+          <t>81339.8 ± 241.9</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>33731.6 ± 196.6</t>
+          <t>56312.6 ± 205.6</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>177.2 ± 7.0</t>
+          <t>307.2 ± 8.2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>22.6 ± 1.6</t>
+          <t>34.5 ± 2.8</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>103.2 ± 4.8</t>
+          <t>182.8 ± 6.1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>47.2 ± 2.6</t>
+          <t>83.6 ± 3.6</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4.2 ± 1.0</t>
+          <t>6.3 ± 1.0</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3614,37 +3614,37 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>48603.2 ± 256.1</t>
+          <t>81155.2 ± 248.3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>33395.2 ± 210.4</t>
+          <t>55750.0 ± 211.3</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>173.8 ± 6.8</t>
+          <t>306.8 ± 7.7</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>22.0 ± 1.3</t>
+          <t>34.8 ± 3.1</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>101.2 ± 4.3</t>
+          <t>181.5 ± 5.8</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>46.8 ± 2.4</t>
+          <t>84.2 ± 3.9</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>3.8 ± 0.9</t>
+          <t>6.3 ± 1.0</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3669,37 +3669,37 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>48465.4 ± 253.0</t>
+          <t>80923.1 ± 240.9</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>33043.4 ± 210.5</t>
+          <t>55144.9 ± 203.0</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>170.2 ± 6.6</t>
+          <t>302.4 ± 8.2</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>20.8 ± 1.1</t>
+          <t>34.8 ± 3.2</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>98.4 ± 4.7</t>
+          <t>178.2 ± 5.8</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>46.8 ± 2.0</t>
+          <t>83.1 ± 3.6</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>4.2 ± 0.9</t>
+          <t>6.3 ± 1.0</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3724,37 +3724,37 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>48377.0 ± 256.6</t>
+          <t>80750.9 ± 246.1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>32746.4 ± 212.5</t>
+          <t>54635.7 ± 204.7</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>168.6 ± 7.5</t>
+          <t>298.8 ± 8.4</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>21.4 ± 0.3</t>
+          <t>34.1 ± 3.2</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>97.6 ± 5.3</t>
+          <t>176.2 ± 6.0</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>45.6 ± 2.8</t>
+          <t>82.0 ± 3.4</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4.0 ± 0.8</t>
+          <t>6.5 ± 1.0</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3779,37 +3779,37 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>48266.0 ± 251.7</t>
+          <t>80561.5 ± 252.2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>32436.2 ± 199.0</t>
+          <t>54114.6 ± 206.0</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>167.0 ± 6.4</t>
+          <t>295.8 ± 8.1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>21.2 ± 0.4</t>
+          <t>33.3 ± 2.9</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>96.0 ± 4.6</t>
+          <t>174.3 ± 5.8</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>45.8 ± 2.9</t>
+          <t>81.6 ± 3.5</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>4.0 ± 0.8</t>
+          <t>6.5 ± 1.1</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3834,37 +3834,37 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>48155.0 ± 253.8</t>
+          <t>80365.6 ± 248.6</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>32142.4 ± 203.2</t>
+          <t>53623.2 ± 200.9</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>163.4 ± 6.1</t>
+          <t>291.8 ± 7.8</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20.2 ± 0.2</t>
+          <t>33.1 ± 3.0</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>93.8 ± 3.8</t>
+          <t>171.6 ± 5.6</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>45.6 ± 3.2</t>
+          <t>80.6 ± 3.3</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>3.8 ± 0.5</t>
+          <t>6.5 ± 1.0</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3889,37 +3889,37 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>48064.2 ± 258.6</t>
+          <t>80227.2 ± 250.1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>31908.2 ± 194.6</t>
+          <t>53234.9 ± 195.8</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>162.8 ± 5.9</t>
+          <t>288.9 ± 8.3</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>19.8 ± 0.2</t>
+          <t>33.0 ± 3.0</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>93.8 ± 3.8</t>
+          <t>170.2 ± 5.9</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>45.2 ± 3.0</t>
+          <t>79.4 ± 3.4</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>4.0 ± 0.5</t>
+          <t>6.4 ± 1.0</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3944,37 +3944,37 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>47975.8 ± 260.9</t>
+          <t>80113.7 ± 250.4</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>31675.0 ± 191.6</t>
+          <t>52870.3 ± 196.9</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>161.8 ± 5.7</t>
+          <t>285.4 ± 9.1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>19.8 ± 0.8</t>
+          <t>32.7 ± 3.0</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>94.2 ± 3.8</t>
+          <t>168.3 ± 6.2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>44.0 ± 3.2</t>
+          <t>78.1 ± 3.5</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>3.8 ± 0.3</t>
+          <t>6.2 ± 0.9</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3999,37 +3999,37 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>47936.0 ± 256.1</t>
+          <t>80036.4 ± 249.1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>31512.4 ± 193.7</t>
+          <t>52585.6 ± 197.0</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>158.8 ± 5.8</t>
+          <t>282.4 ± 9.4</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>19.2 ± 0.8</t>
+          <t>32.2 ± 3.1</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>92.6 ± 3.2</t>
+          <t>165.9 ± 6.3</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>43.2 ± 3.1</t>
+          <t>78.1 ± 3.6</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>3.8 ± 0.3</t>
+          <t>6.1 ± 0.9</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4054,37 +4054,37 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>47824.4 ± 254.0</t>
+          <t>79874.2 ± 248.9</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>31298.2 ± 183.9</t>
+          <t>52244.2 ± 196.5</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>156.0 ± 5.6</t>
+          <t>279.9 ± 9.3</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>18.6 ± 0.5</t>
+          <t>32.1 ± 3.0</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>91.6 ± 2.7</t>
+          <t>164.9 ± 6.1</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>42.4 ± 3.2</t>
+          <t>76.8 ± 3.8</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>3.4 ± 0.2</t>
+          <t>6.1 ± 0.9</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4109,37 +4109,37 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>47682.8 ± 250.4</t>
+          <t>79680.7 ± 247.9</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>31063.4 ± 178.2</t>
+          <t>51889.7 ± 195.1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>153.2 ± 5.4</t>
+          <t>276.9 ± 9.0</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>18.8 ± 0.7</t>
+          <t>32.2 ± 3.1</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>89.4 ± 2.4</t>
+          <t>162.9 ± 5.9</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>41.8 ± 3.3</t>
+          <t>75.7 ± 3.6</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>3.2 ± 0.3</t>
+          <t>6.1 ± 0.9</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4164,37 +4164,37 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>47577.4 ± 253.0</t>
+          <t>79497.0 ± 248.9</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>30881.6 ± 171.6</t>
+          <t>51532.0 ± 192.6</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>149.8 ± 5.2</t>
+          <t>273.9 ± 8.6</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>18.4 ± 0.8</t>
+          <t>31.8 ± 3.1</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>87.2 ± 1.8</t>
+          <t>160.9 ± 5.5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>41.2 ± 3.4</t>
+          <t>75.2 ± 3.4</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>3.0 ± 0.4</t>
+          <t>6.1 ± 0.9</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4219,37 +4219,37 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>47506.2 ± 241.9</t>
+          <t>79313.3 ± 248.3</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>30686.2 ± 164.1</t>
+          <t>51154.2 ± 194.7</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>149.6 ± 4.9</t>
+          <t>270.1 ± 8.9</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>18.6 ± 0.8</t>
+          <t>31.1 ± 3.2</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>86.8 ± 2.1</t>
+          <t>158.3 ± 5.7</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>41.6 ± 3.4</t>
+          <t>74.5 ± 3.1</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2.6 ± 0.5</t>
+          <t>6.1 ± 0.9</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4274,37 +4274,37 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>47400.6 ± 238.8</t>
+          <t>79111.4 ± 252.0</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>30481.2 ± 159.0</t>
+          <t>50765.4 ± 197.5</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>148.0 ± 4.9</t>
+          <t>266.4 ± 9.3</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>17.2 ± 0.4</t>
+          <t>30.6 ± 3.1</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>86.8 ± 1.9</t>
+          <t>155.7 ± 6.3</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>41.4 ± 3.7</t>
+          <t>73.9 ± 2.7</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2.6 ± 0.5</t>
+          <t>6.2 ± 0.9</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4329,37 +4329,37 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>47102.2 ± 236.0</t>
+          <t>78626.6 ± 251.7</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>30235.4 ± 154.2</t>
+          <t>50374.8 ± 192.3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>145.2 ± 4.9</t>
+          <t>263.9 ± 9.4</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>16.6 ± 0.4</t>
+          <t>30.1 ± 3.1</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>85.8 ± 2.4</t>
+          <t>154.9 ± 6.2</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>40.2 ± 3.5</t>
+          <t>72.7 ± 2.8</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2.6 ± 0.5</t>
+          <t>6.3 ± 0.8</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4384,37 +4384,37 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>46797.8 ± 247.4</t>
+          <t>78141.9 ± 254.5</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>29986.4 ± 158.1</t>
+          <t>49943.5 ± 194.5</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>144.8 ± 4.5</t>
+          <t>260.7 ± 8.7</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>17.0 ± 0.4</t>
+          <t>29.9 ± 3.2</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>85.8 ± 2.0</t>
+          <t>153.2 ± 5.9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>39.6 ± 3.7</t>
+          <t>71.8 ± 2.5</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2.4 ± 0.4</t>
+          <t>5.8 ± 0.7</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4439,37 +4439,37 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>46639.6 ± 247.9</t>
+          <t>77858.4 ± 255.9</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>29751.4 ± 167.9</t>
+          <t>49524.4 ± 192.4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>144.0 ± 3.8</t>
+          <t>258.4 ± 8.6</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>17.2 ± 0.9</t>
+          <t>29.5 ± 3.2</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>84.6 ± 1.8</t>
+          <t>151.6 ± 5.8</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>39.8 ± 3.2</t>
+          <t>71.5 ± 2.4</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2.4 ± 0.4</t>
+          <t>5.8 ± 0.7</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4494,37 +4494,37 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>46537.0 ± 258.9</t>
+          <t>77724.4 ± 253.9</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>29544.0 ± 168.6</t>
+          <t>49228.8 ± 190.0</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>144.4 ± 3.9</t>
+          <t>255.6 ± 8.6</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>17.4 ± 1.0</t>
+          <t>29.2 ± 3.2</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>84.8 ± 1.5</t>
+          <t>149.6 ± 6.1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>39.6 ± 3.7</t>
+          <t>71.1 ± 2.4</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2.6 ± 0.3</t>
+          <t>5.7 ± 0.8</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4549,37 +4549,37 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>46322.2 ± 259.1</t>
+          <t>77320.8 ± 249.3</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>29251.4 ± 171.1</t>
+          <t>48782.2 ± 185.2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>144.4 ± 4.0</t>
+          <t>253.6 ± 9.1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>17.6 ± 0.7</t>
+          <t>29.0 ± 3.2</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>84.2 ± 1.8</t>
+          <t>148.0 ± 6.4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>40.0 ± 3.7</t>
+          <t>71.0 ± 2.7</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2.6 ± 0.3</t>
+          <t>5.7 ± 0.7</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4604,37 +4604,37 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>46099.2 ± 267.6</t>
+          <t>76904.6 ± 257.4</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>28960.2 ± 180.8</t>
+          <t>48319.3 ± 186.7</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>141.8 ± 3.2</t>
+          <t>250.4 ± 9.0</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>18.0 ± 0.7</t>
+          <t>28.9 ± 3.3</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>82.4 ± 1.6</t>
+          <t>146.0 ± 6.2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>38.8 ± 3.4</t>
+          <t>70.0 ± 2.4</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2.6 ± 0.2</t>
+          <t>5.5 ± 0.7</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4659,37 +4659,37 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>45811.2 ± 268.7</t>
+          <t>76415.4 ± 254.3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>28654.8 ± 178.5</t>
+          <t>47803.2 ± 183.3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>141.8 ± 3.4</t>
+          <t>246.7 ± 8.9</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>18.0 ± 0.8</t>
+          <t>28.1 ± 3.3</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>82.2 ± 1.9</t>
+          <t>143.9 ± 6.6</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>39.0 ± 3.3</t>
+          <t>69.2 ± 2.2</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2.6 ± 0.2</t>
+          <t>5.5 ± 0.8</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4714,37 +4714,37 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>45486.6 ± 262.8</t>
+          <t>75907.6 ± 257.6</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>28327.6 ± 172.1</t>
+          <t>47283.8 ± 186.1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>140.0 ± 4.0</t>
+          <t>244.7 ± 8.6</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>18.0 ± 1.1</t>
+          <t>28.2 ± 3.2</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>80.6 ± 2.5</t>
+          <t>142.2 ± 6.7</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>38.8 ± 3.0</t>
+          <t>69.0 ± 2.0</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2.6 ± 0.2</t>
+          <t>5.3 ± 0.7</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4769,37 +4769,37 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>45179.0 ± 265.7</t>
+          <t>75366.9 ± 258.8</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>28008.0 ± 173.4</t>
+          <t>46765.4 ± 183.6</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>138.8 ± 3.9</t>
+          <t>241.9 ± 8.3</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>17.6 ± 1.1</t>
+          <t>27.3 ± 3.2</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>80.4 ± 2.4</t>
+          <t>141.0 ± 6.5</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>38.2 ± 3.0</t>
+          <t>68.5 ± 1.6</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2.6 ± 0.2</t>
+          <t>5.1 ± 0.8</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4824,37 +4824,37 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>44844.2 ± 258.6</t>
+          <t>74823.0 ± 256.8</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>27698.4 ± 172.2</t>
+          <t>46232.3 ± 183.6</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>137.0 ± 4.5</t>
+          <t>240.1 ± 7.9</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>17.4 ± 1.1</t>
+          <t>27.2 ± 3.1</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>78.8 ± 2.6</t>
+          <t>139.2 ± 5.9</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>37.8 ± 3.2</t>
+          <t>68.5 ± 2.0</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>3.0 ± 0.0</t>
+          <t>5.2 ± 0.8</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4879,37 +4879,37 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>44541.8 ± 266.9</t>
+          <t>74280.2 ± 258.7</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>27399.8 ± 170.9</t>
+          <t>45698.2 ± 182.3</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>136.6 ± 5.1</t>
+          <t>237.2 ± 7.9</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>16.8 ± 0.9</t>
+          <t>26.9 ± 3.0</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>78.0 ± 3.0</t>
+          <t>136.9 ± 5.8</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>38.8 ± 3.5</t>
+          <t>68.2 ± 1.9</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>3.0 ± 0.0</t>
+          <t>5.3 ± 0.8</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4934,37 +4934,37 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>44167.6 ± 262.7</t>
+          <t>73654.5 ± 263.3</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>27056.4 ± 168.0</t>
+          <t>45135.2 ± 175.3</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>134.2 ± 5.4</t>
+          <t>232.9 ± 7.5</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>16.6 ± 0.7</t>
+          <t>26.3 ± 3.1</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>76.6 ± 3.1</t>
+          <t>134.7 ± 5.6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>38.0 ± 3.3</t>
+          <t>66.8 ± 2.0</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>3.0 ± 0.0</t>
+          <t>5.2 ± 0.8</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4989,37 +4989,37 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>43758.0 ± 265.6</t>
+          <t>73019.0 ± 261.3</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>26721.8 ± 172.1</t>
+          <t>44536.8 ± 175.9</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>131.8 ± 5.3</t>
+          <t>230.1 ± 7.4</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>17.2 ± 0.5</t>
+          <t>26.3 ± 2.9</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>74.2 ± 3.5</t>
+          <t>132.3 ± 5.4</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>37.4 ± 3.0</t>
+          <t>66.2 ± 1.9</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>3.0 ± 0.0</t>
+          <t>5.2 ± 0.8</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5044,37 +5044,37 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>43379.4 ± 267.5</t>
+          <t>72382.6 ± 264.2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>26339.0 ± 174.7</t>
+          <t>43909.6 ± 171.5</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>128.2 ± 5.2</t>
+          <t>225.7 ± 7.3</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>17.2 ± 0.5</t>
+          <t>25.6 ± 2.9</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>73.4 ± 3.4</t>
+          <t>129.7 ± 5.2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>34.6 ± 2.7</t>
+          <t>65.0 ± 1.8</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>3.0 ± 0.0</t>
+          <t>5.3 ± 0.9</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5099,37 +5099,37 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>43026.2 ± 271.0</t>
+          <t>71742.6 ± 262.5</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>25949.4 ± 184.4</t>
+          <t>43251.9 ± 169.4</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>126.8 ± 5.2</t>
+          <t>220.7 ± 6.7</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>16.8 ± 0.7</t>
+          <t>25.3 ± 2.9</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>72.6 ± 3.6</t>
+          <t>126.5 ± 4.8</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>34.4 ± 2.5</t>
+          <t>63.8 ± 1.9</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>3.0 ± 0.0</t>
+          <t>5.2 ± 1.0</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5154,37 +5154,37 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>42639.4 ± 272.8</t>
+          <t>71115.7 ± 257.4</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>25527.6 ± 178.3</t>
+          <t>42568.9 ± 166.9</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>123.8 ± 4.7</t>
+          <t>216.4 ± 6.1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>16.4 ± 0.9</t>
+          <t>25.1 ± 2.8</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>70.4 ± 3.5</t>
+          <t>123.7 ± 4.2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>34.2 ± 2.3</t>
+          <t>62.7 ± 1.7</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2.8 ± 0.2</t>
+          <t>5.0 ± 0.9</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5209,37 +5209,37 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>42259.0 ± 272.5</t>
+          <t>70481.7 ± 261.5</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>25097.4 ± 175.1</t>
+          <t>41862.9 ± 169.8</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>120.6 ± 4.4</t>
+          <t>210.5 ± 5.8</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>16.0 ± 0.9</t>
+          <t>24.4 ± 2.6</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>69.6 ± 3.6</t>
+          <t>120.3 ± 4.0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>32.0 ± 2.2</t>
+          <t>61.2 ± 1.6</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>3.0 ± 0.0</t>
+          <t>4.5 ± 1.0</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5264,37 +5264,37 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>41901.8 ± 270.9</t>
+          <t>69860.9 ± 258.6</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>24691.0 ± 170.8</t>
+          <t>41137.1 ± 165.6</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>116.2 ± 5.1</t>
+          <t>206.8 ± 6.3</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>15.6 ± 0.7</t>
+          <t>23.9 ± 2.7</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>66.0 ± 4.0</t>
+          <t>117.9 ± 4.1</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>31.8 ± 2.0</t>
+          <t>60.4 ± 1.8</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2.8 ± 0.2</t>
+          <t>4.6 ± 0.9</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5319,37 +5319,37 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>41519.2 ± 262.9</t>
+          <t>69209.9 ± 254.3</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>24257.8 ± 166.3</t>
+          <t>40440.7 ± 162.8</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>112.2 ± 5.4</t>
+          <t>202.6 ± 5.8</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>14.8 ± 0.9</t>
+          <t>23.6 ± 2.6</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>64.0 ± 4.1</t>
+          <t>116.1 ± 3.9</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>30.6 ± 2.3</t>
+          <t>58.5 ± 1.8</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2.8 ± 0.2</t>
+          <t>4.4 ± 1.0</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5374,37 +5374,37 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>41148.4 ± 259.9</t>
+          <t>68563.6 ± 249.0</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>23838.4 ± 159.8</t>
+          <t>39723.9 ± 154.7</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>111.4 ± 5.7</t>
+          <t>197.0 ± 5.9</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>14.6 ± 0.8</t>
+          <t>22.9 ± 2.4</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>63.4 ± 4.1</t>
+          <t>112.8 ± 4.1</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>30.6 ± 2.4</t>
+          <t>57.0 ± 1.7</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2.8 ± 0.2</t>
+          <t>4.2 ± 0.9</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -5429,37 +5429,37 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>40770.0 ± 257.0</t>
+          <t>67919.8 ± 248.5</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>23421.0 ± 152.5</t>
+          <t>39026.1 ± 153.1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>110.4 ± 5.8</t>
+          <t>193.4 ± 5.9</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>14.8 ± 0.8</t>
+          <t>22.2 ± 2.3</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>62.4 ± 4.0</t>
+          <t>110.8 ± 4.3</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>30.4 ± 2.4</t>
+          <t>56.3 ± 1.7</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2.8 ± 0.2</t>
+          <t>4.1 ± 0.9</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -5484,37 +5484,37 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>40405.0 ± 244.9</t>
+          <t>67293.9 ± 244.8</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>23035.8 ± 142.5</t>
+          <t>38373.7 ± 152.3</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>108.0 ± 6.1</t>
+          <t>188.7 ± 5.6</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>15.2 ± 0.9</t>
+          <t>22.0 ± 2.1</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.0 ± 4.4</t>
+          <t>108.2 ± 4.3</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>29.0 ± 2.3</t>
+          <t>54.5 ± 1.6</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2.8 ± 0.2</t>
+          <t>4.0 ± 0.9</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -5539,37 +5539,37 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>40006.0 ± 235.1</t>
+          <t>66628.9 ± 236.8</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>22650.4 ± 139.9</t>
+          <t>37755.9 ± 152.4</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>106.6 ± 5.5</t>
+          <t>184.8 ± 6.3</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>15.2 ± 1.0</t>
+          <t>21.6 ± 2.0</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>60.4 ± 3.9</t>
+          <t>105.8 ± 4.6</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>28.0 ± 2.2</t>
+          <t>53.5 ± 2.0</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>3.0 ± 0.3</t>
+          <t>3.9 ± 0.9</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -5594,37 +5594,37 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>39619.4 ± 229.5</t>
+          <t>65992.7 ± 233.9</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>22365.0 ± 133.8</t>
+          <t>37238.2 ± 145.6</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>103.0 ± 4.6</t>
+          <t>181.9 ± 6.8</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>14.4 ± 1.0</t>
+          <t>21.4 ± 1.9</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>57.8 ± 3.4</t>
+          <t>103.6 ± 4.8</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>27.6 ± 2.1</t>
+          <t>53.1 ± 2.2</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>3.2 ± 0.3</t>
+          <t>3.8 ± 0.9</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -5649,37 +5649,37 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>39232.4 ± 226.7</t>
+          <t>65359.4 ± 230.5</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>22110.4 ± 132.2</t>
+          <t>36807.2 ± 145.2</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>100.4 ± 4.3</t>
+          <t>178.8 ± 6.2</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>13.2 ± 1.2</t>
+          <t>20.7 ± 1.9</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>57.0 ± 3.2</t>
+          <t>102.0 ± 4.6</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>27.0 ± 2.0</t>
+          <t>52.5 ± 1.8</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>3.2 ± 0.3</t>
+          <t>3.6 ± 0.9</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -5704,37 +5704,37 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>38849.8 ± 227.3</t>
+          <t>64720.0 ± 232.0</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>21833.0 ± 126.1</t>
+          <t>36376.4 ± 141.8</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>97.8 ± 4.7</t>
+          <t>175.6 ± 5.7</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>13.0 ± 1.2</t>
+          <t>20.2 ± 1.9</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>55.6 ± 3.3</t>
+          <t>100.2 ± 4.3</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>26.6 ± 2.0</t>
+          <t>51.6 ± 2.0</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2.6 ± 0.2</t>
+          <t>3.5 ± 0.8</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5759,37 +5759,37 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>38478.2 ± 212.7</t>
+          <t>64092.4 ± 228.7</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>21578.0 ± 124.9</t>
+          <t>35951.9 ± 137.2</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>95.8 ± 4.8</t>
+          <t>172.8 ± 5.7</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>12.4 ± 1.1</t>
+          <t>19.8 ± 1.9</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>53.8 ± 3.0</t>
+          <t>98.5 ± 4.3</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>27.0 ± 1.9</t>
+          <t>51.0 ± 1.8</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2.6 ± 0.2</t>
+          <t>3.4 ± 0.8</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5814,37 +5814,37 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>38102.0 ± 208.9</t>
+          <t>63493.6 ± 225.5</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>21348.6 ± 117.3</t>
+          <t>35598.4 ± 137.5</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>92.0 ± 4.7</t>
+          <t>169.8 ± 5.1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>12.0 ± 1.1</t>
+          <t>19.8 ± 1.7</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>52.4 ± 2.9</t>
+          <t>96.3 ± 3.9</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>25.2 ± 1.7</t>
+          <t>50.5 ± 1.5</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2.4 ± 0.2</t>
+          <t>3.3 ± 0.8</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5869,37 +5869,37 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>37745.0 ± 206.0</t>
+          <t>62903.7 ± 228.9</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>21151.2 ± 114.6</t>
+          <t>35275.6 ± 137.3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>90.8 ± 4.7</t>
+          <t>168.9 ± 5.5</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>11.4 ± 1.0</t>
+          <t>19.6 ± 1.9</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>52.4 ± 3.2</t>
+          <t>95.2 ± 3.9</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>25.0 ± 2.0</t>
+          <t>50.6 ± 1.6</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2.0 ± 0.3</t>
+          <t>3.4 ± 0.8</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5924,37 +5924,37 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>37368.0 ± 201.2</t>
+          <t>62283.5 ± 226.3</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>21017.8 ± 115.2</t>
+          <t>35062.7 ± 138.9</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>91.0 ± 4.5</t>
+          <t>167.3 ± 5.5</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>10.6 ± 1.0</t>
+          <t>19.6 ± 1.8</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>52.2 ± 3.4</t>
+          <t>94.2 ± 3.9</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>26.2 ± 1.9</t>
+          <t>50.2 ± 1.4</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2.0 ± 0.3</t>
+          <t>3.2 ± 0.8</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5979,37 +5979,37 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>36982.6 ± 202.4</t>
+          <t>61704.0 ± 224.3</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>20936.4 ± 111.2</t>
+          <t>34955.2 ± 141.6</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>88.8 ± 4.6</t>
+          <t>166.9 ± 5.5</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>10.2 ± 1.1</t>
+          <t>19.4 ± 1.7</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>51.8 ± 3.7</t>
+          <t>93.5 ± 3.9</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>25.0 ± 1.8</t>
+          <t>50.9 ± 1.7</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1.8 ± 0.3</t>
+          <t>3.1 ± 0.7</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6034,37 +6034,37 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>36638.2 ± 201.4</t>
+          <t>61096.5 ± 226.8</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>20896.6 ± 110.0</t>
+          <t>34855.2 ± 147.2</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>89.2 ± 4.5</t>
+          <t>165.6 ± 5.6</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>10.4 ± 1.0</t>
+          <t>19.1 ± 1.7</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>52.0 ± 3.2</t>
+          <t>92.9 ± 4.1</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>25.0 ± 2.0</t>
+          <t>50.5 ± 1.8</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>1.8 ± 0.3</t>
+          <t>3.1 ± 0.7</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6089,37 +6089,37 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>36272.6 ± 198.7</t>
+          <t>60498.8 ± 226.1</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>20839.0 ± 119.1</t>
+          <t>34744.1 ± 149.0</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>90.2 ± 4.4</t>
+          <t>165.8 ± 5.5</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>10.6 ± 1.0</t>
+          <t>19.1 ± 1.7</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>52.8 ± 3.0</t>
+          <t>92.5 ± 4.3</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>25.2 ± 1.9</t>
+          <t>51.0 ± 1.7</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1.6 ± 0.3</t>
+          <t>3.1 ± 0.8</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6144,37 +6144,37 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>35902.6 ± 198.4</t>
+          <t>59901.9 ± 226.0</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>20736.6 ± 118.5</t>
+          <t>34582.0 ± 148.1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>89.6 ± 4.3</t>
+          <t>164.6 ± 5.6</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>10.2 ± 1.1</t>
+          <t>18.9 ± 1.7</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>52.8 ± 2.6</t>
+          <t>91.3 ± 4.5</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>25.0 ± 1.9</t>
+          <t>51.0 ± 1.7</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>1.6 ± 0.3</t>
+          <t>3.2 ± 0.8</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6199,37 +6199,37 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>35537.6 ± 200.5</t>
+          <t>59303.8 ± 232.5</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>20620.4 ± 114.5</t>
+          <t>34366.8 ± 152.4</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>89.2 ± 4.2</t>
+          <t>162.3 ± 5.7</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>10.4 ± 1.0</t>
+          <t>18.6 ± 1.7</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>52.6 ± 2.1</t>
+          <t>89.8 ± 4.2</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>24.6 ± 2.3</t>
+          <t>50.9 ± 2.1</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>1.6 ± 0.3</t>
+          <t>3.0 ± 0.7</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6254,37 +6254,37 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>35177.8 ± 202.6</t>
+          <t>58688.8 ± 236.1</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>20482.8 ± 115.1</t>
+          <t>34172.9 ± 151.6</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>90.8 ± 4.5</t>
+          <t>161.2 ± 5.5</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>10.8 ± 1.1</t>
+          <t>18.5 ± 1.8</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>52.4 ± 2.0</t>
+          <t>89.1 ± 4.2</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>26.0 ± 2.5</t>
+          <t>50.5 ± 2.1</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>1.6 ± 0.3</t>
+          <t>3.0 ± 0.7</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -6309,37 +6309,37 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>34819.8 ± 213.0</t>
+          <t>58070.7 ± 236.1</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>20370.0 ± 119.5</t>
+          <t>33964.1 ± 149.3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>90.0 ± 4.8</t>
+          <t>161.4 ± 5.6</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>10.8 ± 1.0</t>
+          <t>18.6 ± 1.8</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>52.6 ± 2.0</t>
+          <t>88.9 ± 4.1</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>24.8 ± 2.5</t>
+          <t>50.8 ± 2.1</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1.8 ± 0.3</t>
+          <t>3.1 ± 0.8</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6364,37 +6364,37 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>34455.8 ± 217.1</t>
+          <t>57436.9 ± 236.8</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>20217.4 ± 119.5</t>
+          <t>33689.1 ± 145.6</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>89.8 ± 4.8</t>
+          <t>160.8 ± 5.4</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>10.6 ± 1.1</t>
+          <t>18.4 ± 1.8</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>51.4 ± 1.9</t>
+          <t>88.8 ± 4.1</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>25.8 ± 2.6</t>
+          <t>50.5 ± 2.0</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>2.0 ± 0.4</t>
+          <t>3.0 ± 0.7</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -6419,37 +6419,37 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>34073.2 ± 220.7</t>
+          <t>56804.1 ± 241.8</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>20034.2 ± 121.2</t>
+          <t>33400.0 ± 153.1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>89.2 ± 4.3</t>
+          <t>159.6 ± 5.6</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>10.2 ± 0.9</t>
+          <t>18.2 ± 1.8</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>52.0 ± 1.7</t>
+          <t>87.8 ± 3.9</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>25.0 ± 2.5</t>
+          <t>50.5 ± 2.1</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>2.0 ± 0.4</t>
+          <t>3.0 ± 0.8</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -6474,37 +6474,37 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>33686.0 ± 211.8</t>
+          <t>56167.8 ± 248.7</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>19829.8 ± 110.9</t>
+          <t>33047.7 ± 156.3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>86.6 ± 4.8</t>
+          <t>156.8 ± 5.3</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>9.6 ± 1.0</t>
+          <t>17.9 ± 1.7</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>50.4 ± 2.2</t>
+          <t>85.8 ± 3.7</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>24.8 ± 2.5</t>
+          <t>50.2 ± 2.3</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1.8 ± 0.3</t>
+          <t>3.0 ± 0.8</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -6529,37 +6529,37 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>33264.0 ± 206.4</t>
+          <t>55531.1 ± 245.2</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>19611.4 ± 114.1</t>
+          <t>32693.9 ± 156.5</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>86.0 ± 5.6</t>
+          <t>154.8 ± 5.5</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>9.6 ± 1.4</t>
+          <t>17.9 ± 1.7</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>49.4 ± 2.5</t>
+          <t>84.7 ± 3.9</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>25.2 ± 2.8</t>
+          <t>49.5 ± 2.2</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>1.8 ± 0.3</t>
+          <t>2.7 ± 0.7</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -6584,37 +6584,37 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>32862.4 ± 202.8</t>
+          <t>54900.5 ± 245.9</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>19391.8 ± 110.5</t>
+          <t>32341.8 ± 161.2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>84.2 ± 5.4</t>
+          <t>152.6 ± 5.0</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>9.6 ± 1.4</t>
+          <t>17.4 ± 1.7</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>48.2 ± 2.2</t>
+          <t>83.3 ± 3.7</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>24.6 ± 2.8</t>
+          <t>49.3 ± 2.1</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>1.8 ± 0.3</t>
+          <t>2.5 ± 0.6</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -6639,37 +6639,37 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>32496.6 ± 212.7</t>
+          <t>54246.8 ± 237.3</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>19154.6 ± 109.7</t>
+          <t>31923.3 ± 154.6</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>83.6 ± 5.7</t>
+          <t>150.7 ± 5.1</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>10.2 ± 1.5</t>
+          <t>17.1 ± 1.8</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>48.2 ± 2.3</t>
+          <t>81.5 ± 3.7</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>23.6 ± 2.8</t>
+          <t>49.3 ± 2.2</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1.6 ± 0.3</t>
+          <t>2.7 ± 0.6</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -6694,37 +6694,37 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>32106.6 ± 204.7</t>
+          <t>53617.2 ± 232.4</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>18886.6 ± 103.0</t>
+          <t>31506.8 ± 152.0</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>83.2 ± 5.2</t>
+          <t>147.8 ± 4.9</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>10.2 ± 1.4</t>
+          <t>16.7 ± 1.8</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>47.4 ± 2.4</t>
+          <t>79.8 ± 3.6</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>23.8 ± 2.5</t>
+          <t>48.6 ± 2.1</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1.8 ± 0.3</t>
+          <t>2.7 ± 0.6</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -6749,37 +6749,37 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>31719.4 ± 199.0</t>
+          <t>52982.8 ± 230.8</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>18583.2 ± 94.2</t>
+          <t>31038.6 ± 149.5</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>82.2 ± 4.9</t>
+          <t>144.6 ± 4.8</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>9.6 ± 1.5</t>
+          <t>16.4 ± 1.8</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>46.0 ± 2.3</t>
+          <t>77.9 ± 3.7</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>24.8 ± 2.4</t>
+          <t>47.6 ± 2.1</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>1.8 ± 0.3</t>
+          <t>2.6 ± 0.6</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -6804,37 +6804,37 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>31356.4 ± 198.0</t>
+          <t>52358.8 ± 232.6</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>18342.6 ± 94.2</t>
+          <t>30622.4 ± 148.1</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>81.8 ± 4.7</t>
+          <t>142.8 ± 4.9</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>9.8 ± 1.8</t>
+          <t>16.1 ± 1.7</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>45.4 ± 2.0</t>
+          <t>76.9 ± 3.7</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>25.0 ± 2.1</t>
+          <t>47.4 ± 2.0</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1.6 ± 0.4</t>
+          <t>2.5 ± 0.6</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -6859,37 +6859,37 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>30975.4 ± 194.9</t>
+          <t>51755.1 ± 236.9</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>18104.2 ± 95.8</t>
+          <t>30218.8 ± 153.4</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>81.4 ± 4.5</t>
+          <t>140.1 ± 4.7</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>9.8 ± 1.7</t>
+          <t>15.9 ± 1.6</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>45.0 ± 1.8</t>
+          <t>75.5 ± 3.9</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>25.0 ± 2.0</t>
+          <t>46.2 ± 2.0</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>1.6 ± 0.4</t>
+          <t>2.5 ± 0.6</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6914,37 +6914,37 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>30603.6 ± 185.2</t>
+          <t>51150.3 ± 229.9</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>17852.8 ± 92.5</t>
+          <t>29826.2 ± 148.5</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>79.8 ± 5.4</t>
+          <t>138.2 ± 4.8</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>9.0 ± 1.8</t>
+          <t>15.8 ± 1.6</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>44.0 ± 2.4</t>
+          <t>74.3 ± 3.8</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>25.2 ± 1.8</t>
+          <t>45.7 ± 2.2</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>1.6 ± 0.4</t>
+          <t>2.4 ± 0.5</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -6969,37 +6969,37 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>30249.6 ± 182.2</t>
+          <t>50549.6 ± 231.7</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>17602.6 ± 96.5</t>
+          <t>29449.4 ± 149.5</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>77.6 ± 4.9</t>
+          <t>135.9 ± 4.5</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>8.8 ± 1.8</t>
+          <t>15.3 ± 1.5</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>42.6 ± 1.8</t>
+          <t>73.1 ± 3.3</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>24.6 ± 1.6</t>
+          <t>45.2 ± 2.4</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>1.6 ± 0.5</t>
+          <t>2.2 ± 0.5</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7024,37 +7024,37 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>29871.2 ± 185.7</t>
+          <t>49931.6 ± 228.2</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>17360.6 ± 97.4</t>
+          <t>29081.5 ± 146.4</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>75.2 ± 4.3</t>
+          <t>133.7 ± 4.3</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>8.8 ± 1.8</t>
+          <t>15.4 ± 1.6</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>41.6 ± 1.6</t>
+          <t>71.8 ± 3.3</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>23.2 ± 1.5</t>
+          <t>44.3 ± 2.1</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>1.6 ± 0.5</t>
+          <t>2.2 ± 0.5</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7079,37 +7079,37 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>29492.4 ± 189.7</t>
+          <t>49319.3 ± 225.9</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>17121.6 ± 101.9</t>
+          <t>28675.7 ± 147.8</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>73.6 ± 4.2</t>
+          <t>130.8 ± 4.3</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>8.4 ± 1.8</t>
+          <t>15.2 ± 1.4</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>41.2 ± 1.5</t>
+          <t>70.2 ± 3.5</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>22.4 ± 1.3</t>
+          <t>43.2 ± 2.2</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>1.6 ± 0.5</t>
+          <t>2.2 ± 0.5</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7134,37 +7134,37 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>29122.2 ± 181.7</t>
+          <t>48715.8 ± 224.5</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>16911.4 ± 98.1</t>
+          <t>28296.0 ± 146.4</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>72.8 ± 4.6</t>
+          <t>128.5 ± 4.3</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>8.2 ± 1.8</t>
+          <t>14.8 ± 1.4</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>41.2 ± 2.0</t>
+          <t>69.0 ± 3.6</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>22.0 ± 1.3</t>
+          <t>42.6 ± 1.9</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>1.4 ± 0.5</t>
+          <t>2.1 ± 0.5</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7189,37 +7189,37 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>28766.0 ± 181.7</t>
+          <t>48119.5 ± 218.5</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>16697.8 ± 92.2</t>
+          <t>27950.2 ± 144.8</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>73.6 ± 4.8</t>
+          <t>127.2 ± 4.4</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>8.4 ± 1.9</t>
+          <t>14.9 ± 1.3</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>42.0 ± 2.2</t>
+          <t>68.2 ± 3.7</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>21.8 ± 1.2</t>
+          <t>42.0 ± 1.9</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>1.4 ± 0.5</t>
+          <t>2.1 ± 0.5</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7244,37 +7244,37 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>28390.0 ± 180.6</t>
+          <t>47530.3 ± 213.9</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>16446.2 ± 81.7</t>
+          <t>27533.8 ± 148.5</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>72.0 ± 4.4</t>
+          <t>125.3 ± 4.4</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>8.2 ± 1.8</t>
+          <t>15.0 ± 1.3</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>40.8 ± 2.0</t>
+          <t>67.5 ± 3.7</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>21.6 ± 1.4</t>
+          <t>40.8 ± 2.1</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>1.4 ± 0.5</t>
+          <t>2.1 ± 0.5</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -7299,37 +7299,37 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>28023.6 ± 172.2</t>
+          <t>46957.6 ± 213.6</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>16231.0 ± 76.6</t>
+          <t>27204.6 ± 149.7</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>70.2 ± 4.6</t>
+          <t>124.0 ± 4.2</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>8.2 ± 1.9</t>
+          <t>14.8 ± 1.3</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>39.4 ± 2.3</t>
+          <t>67.1 ± 3.5</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>21.4 ± 1.4</t>
+          <t>40.2 ± 2.3</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>1.2 ± 0.6</t>
+          <t>1.9 ± 0.5</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -7354,37 +7354,37 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>27676.8 ± 168.1</t>
+          <t>46382.2 ± 208.7</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>16030.2 ± 69.9</t>
+          <t>26889.8 ± 143.8</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>68.2 ± 4.7</t>
+          <t>122.5 ± 4.4</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>8.0 ± 1.7</t>
+          <t>14.7 ± 1.3</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>38.2 ± 2.3</t>
+          <t>66.6 ± 3.4</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>21.0 ± 1.5</t>
+          <t>39.4 ± 2.4</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>1.0 ± 0.6</t>
+          <t>1.8 ± 0.5</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -7409,37 +7409,37 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>27370.4 ± 161.6</t>
+          <t>45817.2 ± 208.4</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>15870.0 ± 62.7</t>
+          <t>26610.6 ± 142.1</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>68.2 ± 4.5</t>
+          <t>121.1 ± 4.3</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>7.4 ± 1.5</t>
+          <t>14.6 ± 1.3</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>38.4 ± 2.6</t>
+          <t>65.5 ± 3.5</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>21.4 ± 1.5</t>
+          <t>39.2 ± 2.3</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>1.0 ± 0.6</t>
+          <t>1.9 ± 0.5</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -7464,37 +7464,37 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>27061.4 ± 154.0</t>
+          <t>45270.4 ± 210.3</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>15709.0 ± 65.4</t>
+          <t>26330.2 ± 142.2</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>67.8 ± 4.1</t>
+          <t>119.8 ± 4.1</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>7.6 ± 1.5</t>
+          <t>14.4 ± 1.3</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>38.2 ± 2.2</t>
+          <t>64.7 ± 3.5</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>21.2 ± 1.5</t>
+          <t>39.0 ± 2.2</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>0.8 ± 0.5</t>
+          <t>1.8 ± 0.4</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -7519,37 +7519,37 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>26745.4 ± 153.9</t>
+          <t>44732.3 ± 215.8</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>15560.4 ± 65.4</t>
+          <t>26065.3 ± 144.1</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>67.0 ± 3.8</t>
+          <t>118.2 ± 4.1</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>7.6 ± 1.5</t>
+          <t>14.0 ± 1.2</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>37.4 ± 2.1</t>
+          <t>64.1 ± 3.6</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>21.2 ± 1.6</t>
+          <t>38.4 ± 2.0</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>0.8 ± 0.5</t>
+          <t>1.8 ± 0.4</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -7574,37 +7574,37 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>26457.6 ± 146.7</t>
+          <t>44245.7 ± 214.1</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>15406.6 ± 65.3</t>
+          <t>25823.2 ± 140.7</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>68.0 ± 4.1</t>
+          <t>116.8 ± 3.8</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>8.2 ± 1.5</t>
+          <t>13.8 ± 1.1</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>37.2 ± 2.3</t>
+          <t>63.4 ± 3.4</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>21.8 ± 1.8</t>
+          <t>37.6 ± 1.9</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>0.8 ± 0.5</t>
+          <t>1.9 ± 0.4</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -7629,37 +7629,37 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>26190.8 ± 149.0</t>
+          <t>43791.8 ± 212.3</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>15243.6 ± 64.5</t>
+          <t>25578.5 ± 140.2</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>68.6 ± 3.7</t>
+          <t>115.8 ± 4.1</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>7.8 ± 1.5</t>
+          <t>13.7 ± 1.1</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>37.6 ± 2.3</t>
+          <t>62.8 ± 3.6</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>22.4 ± 2.0</t>
+          <t>37.5 ± 2.2</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>0.8 ± 0.5</t>
+          <t>1.9 ± 0.4</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -7684,37 +7684,37 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>25923.6 ± 136.4</t>
+          <t>43350.8 ± 211.4</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>15098.8 ± 63.3</t>
+          <t>25343.5 ± 143.6</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>67.4 ± 3.9</t>
+          <t>116.0 ± 4.3</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>7.6 ± 1.4</t>
+          <t>13.7 ± 1.0</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>36.8 ± 2.4</t>
+          <t>62.2 ± 3.6</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>22.2 ± 1.8</t>
+          <t>38.1 ± 2.2</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>0.8 ± 0.5</t>
+          <t>1.9 ± 0.4</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -7739,37 +7739,37 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>25659.4 ± 121.3</t>
+          <t>42892.2 ± 210.0</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>14963.8 ± 50.6</t>
+          <t>25101.8 ± 142.2</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>66.0 ± 3.6</t>
+          <t>114.7 ± 4.2</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>7.2 ± 1.4</t>
+          <t>13.6 ± 1.1</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>36.2 ± 2.4</t>
+          <t>61.5 ± 3.4</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>21.8 ± 1.8</t>
+          <t>37.7 ± 2.1</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>0.8 ± 0.5</t>
+          <t>1.9 ± 0.4</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -7794,37 +7794,37 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>25403.0 ± 111.0</t>
+          <t>42469.3 ± 209.1</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>14818.2 ± 42.8</t>
+          <t>24868.4 ± 143.1</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>65.4 ± 3.9</t>
+          <t>113.9 ± 4.2</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>7.0 ± 1.2</t>
+          <t>13.6 ± 1.1</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>35.4 ± 2.6</t>
+          <t>61.2 ± 3.6</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>22.4 ± 1.3</t>
+          <t>37.2 ± 1.8</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>0.6 ± 0.5</t>
+          <t>1.9 ± 0.4</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -7849,37 +7849,37 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>25150.6 ± 107.8</t>
+          <t>42049.2 ± 209.2</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>14675.4 ± 39.4</t>
+          <t>24630.2 ± 145.7</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>64.4 ± 4.0</t>
+          <t>113.7 ± 4.1</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>6.8 ± 1.3</t>
+          <t>13.5 ± 1.1</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>34.6 ± 2.9</t>
+          <t>61.1 ± 3.6</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>22.4 ± 1.2</t>
+          <t>37.1 ± 1.8</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>0.6 ± 0.5</t>
+          <t>1.9 ± 0.4</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -7904,37 +7904,37 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>24907.0 ± 110.2</t>
+          <t>41676.2 ± 206.4</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>14530.6 ± 39.6</t>
+          <t>24387.5 ± 145.2</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>63.8 ± 4.6</t>
+          <t>112.2 ± 4.3</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>6.6 ± 1.6</t>
+          <t>13.5 ± 1.2</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>33.6 ± 3.3</t>
+          <t>60.5 ± 3.5</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>23.0 ± 1.0</t>
+          <t>36.2 ± 2.1</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>0.6 ± 0.5</t>
+          <t>1.9 ± 0.4</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -7959,37 +7959,37 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>24675.0 ± 103.4</t>
+          <t>41316.5 ± 209.8</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>14377.2 ± 40.5</t>
+          <t>24147.3 ± 145.6</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>63.0 ± 4.5</t>
+          <t>109.9 ± 4.4</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>6.4 ± 1.5</t>
+          <t>13.2 ± 1.2</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>33.4 ± 3.5</t>
+          <t>59.4 ± 3.5</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>22.6 ± 0.9</t>
+          <t>35.5 ± 2.0</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>0.6 ± 0.5</t>
+          <t>1.9 ± 0.4</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8014,37 +8014,37 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>24468.0 ± 100.6</t>
+          <t>40972.8 ± 213.4</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>14216.4 ± 34.8</t>
+          <t>23918.3 ± 148.8</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>61.6 ± 4.3</t>
+          <t>109.0 ± 4.3</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>6.4 ± 1.5</t>
+          <t>13.2 ± 1.2</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>31.8 ± 3.1</t>
+          <t>58.5 ± 3.6</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>22.4 ± 1.0</t>
+          <t>35.5 ± 1.9</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>1.0 ± 0.4</t>
+          <t>1.8 ± 0.4</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8069,37 +8069,37 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>24258.0 ± 104.8</t>
+          <t>40629.3 ± 217.2</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>14072.2 ± 44.9</t>
+          <t>23667.0 ± 150.9</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>61.2 ± 4.4</t>
+          <t>108.0 ± 4.2</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>6.2 ± 1.6</t>
+          <t>13.2 ± 1.3</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>31.6 ± 3.1</t>
+          <t>58.0 ± 3.5</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>22.4 ± 1.3</t>
+          <t>35.0 ± 2.0</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>1.0 ± 0.4</t>
+          <t>1.7 ± 0.4</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -8124,37 +8124,37 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>24025.2 ± 104.6</t>
+          <t>40247.8 ± 217.2</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>13912.0 ± 43.4</t>
+          <t>23410.4 ± 151.0</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>60.4 ± 4.3</t>
+          <t>106.0 ± 4.3</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>6.2 ± 1.6</t>
+          <t>12.9 ± 1.3</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>30.2 ± 2.7</t>
+          <t>57.4 ± 3.4</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>23.0 ± 1.1</t>
+          <t>34.1 ± 2.1</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>1.0 ± 0.4</t>
+          <t>1.6 ± 0.4</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -8179,37 +8179,37 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>23795.2 ± 99.9</t>
+          <t>39847.2 ± 223.5</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>13746.4 ± 44.8</t>
+          <t>23147.0 ± 151.9</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>58.2 ± 4.1</t>
+          <t>105.2 ± 4.3</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>6.2 ± 1.5</t>
+          <t>13.1 ± 1.4</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>29.4 ± 2.8</t>
+          <t>57.3 ± 3.2</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>21.6 ± 1.1</t>
+          <t>33.3 ± 1.9</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>1.0 ± 0.4</t>
+          <t>1.6 ± 0.5</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8234,37 +8234,37 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>23555.4 ± 101.2</t>
+          <t>39457.1 ± 223.1</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>13582.4 ± 44.9</t>
+          <t>22880.5 ± 151.4</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>57.8 ± 3.7</t>
+          <t>104.2 ± 4.2</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>6.2 ± 1.5</t>
+          <t>12.8 ± 1.4</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>28.4 ± 2.6</t>
+          <t>56.8 ± 3.1</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>22.4 ± 1.2</t>
+          <t>33.1 ± 1.9</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>0.8 ± 0.3</t>
+          <t>1.4 ± 0.4</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -8289,37 +8289,37 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>23316.4 ± 90.6</t>
+          <t>39074.3 ± 221.3</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>13415.8 ± 44.9</t>
+          <t>22623.4 ± 155.4</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>57.2 ± 3.7</t>
+          <t>103.3 ± 3.9</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>6.2 ± 1.4</t>
+          <t>12.6 ± 1.5</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>28.8 ± 2.8</t>
+          <t>56.4 ± 3.0</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>21.4 ± 0.9</t>
+          <t>32.8 ± 1.6</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>0.8 ± 0.3</t>
+          <t>1.6 ± 0.4</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -8344,37 +8344,37 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>23078.6 ± 90.5</t>
+          <t>38664.2 ± 220.0</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>13252.4 ± 45.0</t>
+          <t>22361.2 ± 157.9</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>57.4 ± 4.0</t>
+          <t>102.3 ± 3.7</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>6.2 ± 1.4</t>
+          <t>12.2 ± 1.5</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>29.2 ± 3.1</t>
+          <t>55.7 ± 2.7</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>21.2 ± 1.2</t>
+          <t>33.0 ± 1.7</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>0.8 ± 0.3</t>
+          <t>1.4 ± 0.4</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -8399,37 +8399,37 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>22819.8 ± 91.0</t>
+          <t>38262.4 ± 215.0</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>13085.4 ± 48.4</t>
+          <t>22096.5 ± 156.6</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>57.0 ± 4.0</t>
+          <t>101.5 ± 3.6</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>6.2 ± 1.4</t>
+          <t>12.1 ± 1.5</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>27.8 ± 3.0</t>
+          <t>55.1 ± 2.6</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>22.0 ± 1.3</t>
+          <t>32.9 ± 1.6</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>1.0 ± 0.3</t>
+          <t>1.4 ± 0.4</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -8454,37 +8454,37 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>22559.2 ± 95.5</t>
+          <t>37829.8 ± 215.9</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>12946.8 ± 53.8</t>
+          <t>21842.1 ± 159.4</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>55.8 ± 3.8</t>
+          <t>100.0 ± 3.6</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>6.0 ± 1.5</t>
+          <t>11.9 ± 1.5</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>26.6 ± 2.6</t>
+          <t>54.6 ± 2.6</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>22.4 ± 1.4</t>
+          <t>32.1 ± 1.5</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>0.8 ± 0.3</t>
+          <t>1.4 ± 0.4</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -8509,37 +8509,37 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>22324.2 ± 90.8</t>
+          <t>37400.8 ± 215.8</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>12796.8 ± 50.9</t>
+          <t>21578.5 ± 160.8</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>55.8 ± 3.5</t>
+          <t>98.0 ± 3.7</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>6.2 ± 1.5</t>
+          <t>11.8 ± 1.4</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>27.0 ± 2.4</t>
+          <t>53.5 ± 2.7</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>21.8 ± 1.2</t>
+          <t>31.3 ± 1.5</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>0.8 ± 0.3</t>
+          <t>1.4 ± 0.4</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -8564,37 +8564,37 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>22051.8 ± 79.5</t>
+          <t>36973.0 ± 215.8</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>12621.0 ± 44.9</t>
+          <t>21311.0 ± 159.2</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>55.6 ± 3.6</t>
+          <t>97.0 ± 4.0</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>6.2 ± 1.5</t>
+          <t>11.4 ± 1.4</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>27.2 ± 2.4</t>
+          <t>53.0 ± 2.8</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>21.4 ± 1.1</t>
+          <t>31.4 ± 1.5</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>0.8 ± 0.3</t>
+          <t>1.2 ± 0.3</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -8619,37 +8619,37 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>21788.8 ± 70.1</t>
+          <t>36529.3 ± 216.1</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>12467.2 ± 44.5</t>
+          <t>21037.5 ± 159.5</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>54.4 ± 3.2</t>
+          <t>95.1 ± 3.8</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>6.0 ± 1.4</t>
+          <t>11.4 ± 1.4</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>25.8 ± 2.4</t>
+          <t>51.5 ± 3.0</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>21.8 ± 1.1</t>
+          <t>31.1 ± 1.6</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>0.8 ± 0.3</t>
+          <t>1.1 ± 0.3</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -8674,37 +8674,37 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>21520.6 ± 73.7</t>
+          <t>36100.1 ± 213.9</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>12314.0 ± 45.0</t>
+          <t>20792.8 ± 155.6</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>53.8 ± 3.4</t>
+          <t>95.5 ± 3.9</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>5.8 ± 1.1</t>
+          <t>11.4 ± 1.3</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>25.6 ± 2.6</t>
+          <t>52.0 ± 3.0</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>21.4 ± 1.2</t>
+          <t>30.8 ± 1.7</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>1.0 ± 0.4</t>
+          <t>1.2 ± 0.3</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -8729,37 +8729,37 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>21236.6 ± 69.7</t>
+          <t>35649.2 ± 215.7</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>12176.8 ± 47.5</t>
+          <t>20541.8 ± 161.1</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>54.2 ± 2.8</t>
+          <t>94.0 ± 3.8</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>6.0 ± 1.2</t>
+          <t>11.4 ± 1.4</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>25.8 ± 2.4</t>
+          <t>51.3 ± 2.9</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>21.2 ± 1.4</t>
+          <t>30.0 ± 1.8</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>1.2 ± 0.5</t>
+          <t>1.2 ± 0.3</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -8784,37 +8784,37 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>20976.4 ± 64.1</t>
+          <t>35243.5 ± 212.3</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>12013.0 ± 45.1</t>
+          <t>20314.3 ± 158.9</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>52.6 ± 2.4</t>
+          <t>92.5 ± 3.7</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>5.8 ± 1.1</t>
+          <t>11.0 ± 1.3</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>24.6 ± 2.1</t>
+          <t>50.8 ± 2.9</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>21.0 ± 1.5</t>
+          <t>29.6 ± 1.8</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>1.2 ± 0.5</t>
+          <t>1.1 ± 0.3</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -8839,37 +8839,37 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>20727.2 ± 59.1</t>
+          <t>34824.1 ± 210.6</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>11872.6 ± 38.2</t>
+          <t>20089.0 ± 158.3</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>52.6 ± 2.0</t>
+          <t>91.6 ± 3.9</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>5.6 ± 1.0</t>
+          <t>11.1 ± 1.3</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>24.4 ± 1.9</t>
+          <t>50.3 ± 2.7</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>21.4 ± 1.4</t>
+          <t>29.2 ± 1.8</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>1.2 ± 0.5</t>
+          <t>1.1 ± 0.3</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -8894,37 +8894,37 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>20471.2 ± 62.5</t>
+          <t>34424.4 ± 210.0</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>11724.8 ± 35.7</t>
+          <t>19850.7 ± 156.1</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>50.8 ± 1.8</t>
+          <t>89.5 ± 3.8</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>5.2 ± 1.0</t>
+          <t>10.8 ± 1.3</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>23.2 ± 1.8</t>
+          <t>49.4 ± 2.6</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>21.0 ± 1.4</t>
+          <t>28.3 ± 1.9</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>1.4 ± 0.6</t>
+          <t>1.1 ± 0.3</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -8949,37 +8949,37 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>20216.4 ± 66.4</t>
+          <t>34037.1 ± 210.6</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>11590.0 ± 38.0</t>
+          <t>19627.7 ± 151.9</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>49.4 ± 1.8</t>
+          <t>88.6 ± 3.9</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>5.0 ± 0.9</t>
+          <t>10.7 ± 1.2</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>22.2 ± 1.8</t>
+          <t>48.5 ± 2.5</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20.6 ± 1.4</t>
+          <t>28.2 ± 2.1</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>1.6 ± 0.5</t>
+          <t>1.1 ± 0.3</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9004,37 +9004,37 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>19973.2 ± 54.7</t>
+          <t>33647.6 ± 212.0</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>11466.0 ± 29.9</t>
+          <t>19401.1 ± 150.6</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>48.6 ± 1.4</t>
+          <t>87.2 ± 3.8</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>4.8 ± 0.9</t>
+          <t>10.4 ± 1.2</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>21.4 ± 1.9</t>
+          <t>48.0 ± 2.4</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20.6 ± 1.3</t>
+          <t>27.5 ± 2.2</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>1.8 ± 0.5</t>
+          <t>1.2 ± 0.3</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -9059,37 +9059,37 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>19742.6 ± 51.8</t>
+          <t>33261.8 ± 212.2</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>11331.2 ± 23.3</t>
+          <t>19195.2 ± 151.6</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>48.2 ± 1.9</t>
+          <t>86.3 ± 3.8</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>4.8 ± 0.9</t>
+          <t>10.3 ± 1.1</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>21.4 ± 1.9</t>
+          <t>47.5 ± 2.3</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20.2 ± 1.3</t>
+          <t>27.2 ± 2.3</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>1.8 ± 0.5</t>
+          <t>1.2 ± 0.3</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -9114,37 +9114,37 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>19533.2 ± 50.4</t>
+          <t>32872.3 ± 211.9</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>11216.4 ± 19.5</t>
+          <t>18980.5 ± 151.3</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>47.4 ± 1.8</t>
+          <t>85.0 ± 3.9</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>4.8 ± 0.9</t>
+          <t>10.2 ± 1.2</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>21.2 ± 1.9</t>
+          <t>46.6 ± 2.2</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>19.8 ± 1.3</t>
+          <t>26.9 ± 2.4</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>1.6 ± 0.4</t>
+          <t>1.3 ± 0.3</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -9169,37 +9169,37 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>19302.6 ± 46.3</t>
+          <t>32505.5 ± 208.8</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>11091.0 ± 16.4</t>
+          <t>18776.7 ± 147.5</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>47.6 ± 2.1</t>
+          <t>84.8 ± 3.8</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>4.2 ± 0.8</t>
+          <t>10.0 ± 1.2</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>21.4 ± 2.1</t>
+          <t>46.6 ± 2.1</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20.4 ± 1.2</t>
+          <t>27.0 ± 2.2</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>1.6 ± 0.4</t>
+          <t>1.2 ± 0.3</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -9224,37 +9224,37 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>19072.0 ± 50.5</t>
+          <t>32115.7 ± 213.7</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>10956.8 ± 28.7</t>
+          <t>18578.0 ± 143.0</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>46.4 ± 1.7</t>
+          <t>83.7 ± 3.8</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>3.8 ± 0.8</t>
+          <t>9.9 ± 1.2</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>21.6 ± 1.8</t>
+          <t>46.1 ± 2.1</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>19.4 ± 1.1</t>
+          <t>26.4 ± 2.2</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>1.6 ± 0.4</t>
+          <t>1.2 ± 0.3</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -9279,37 +9279,37 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>18835.8 ± 56.8</t>
+          <t>31767.0 ± 212.1</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>10830.6 ± 30.9</t>
+          <t>18383.7 ± 141.0</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>45.6 ± 1.4</t>
+          <t>82.3 ± 3.9</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>3.8 ± 0.8</t>
+          <t>9.8 ± 1.2</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>21.2 ± 1.8</t>
+          <t>45.0 ± 2.3</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>19.0 ± 1.0</t>
+          <t>26.2 ± 2.3</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>1.6 ± 0.4</t>
+          <t>1.2 ± 0.3</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -9334,37 +9334,37 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>18622.0 ± 52.6</t>
+          <t>31416.8 ± 206.8</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>10706.4 ± 26.9</t>
+          <t>18190.0 ± 139.8</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>46.2 ± 1.6</t>
+          <t>81.0 ± 3.4</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>4.0 ± 0.8</t>
+          <t>9.8 ± 1.3</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>21.6 ± 1.7</t>
+          <t>44.0 ± 1.8</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>19.0 ± 1.3</t>
+          <t>25.8 ± 2.1</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>1.6 ± 0.4</t>
+          <t>1.3 ± 0.3</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -9389,37 +9389,37 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>18413.8 ± 49.8</t>
+          <t>31090.7 ± 204.8</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>10586.0 ± 27.2</t>
+          <t>18006.5 ± 138.3</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>45.0 ± 1.5</t>
+          <t>80.1 ± 3.5</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>3.8 ± 0.9</t>
+          <t>9.6 ± 1.3</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>21.6 ± 1.7</t>
+          <t>43.4 ± 1.9</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>18.2 ± 1.0</t>
+          <t>25.8 ± 2.1</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>1.4 ± 0.3</t>
+          <t>1.3 ± 0.3</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -9444,37 +9444,37 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>18211.4 ± 50.7</t>
+          <t>30761.8 ± 207.0</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>10463.8 ± 32.6</t>
+          <t>17811.0 ± 137.5</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>45.0 ± 1.3</t>
+          <t>78.8 ± 3.3</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>3.8 ± 0.9</t>
+          <t>9.7 ± 1.2</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>21.8 ± 1.9</t>
+          <t>42.5 ± 2.0</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>18.0 ± 0.9</t>
+          <t>25.3 ± 2.0</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>1.4 ± 0.3</t>
+          <t>1.2 ± 0.3</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -9499,32 +9499,32 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>18033.2 ± 49.9</t>
+          <t>30447.6 ± 206.6</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>10356.2 ± 33.5</t>
+          <t>17620.0 ± 141.4</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>44.0 ± 1.1</t>
+          <t>78.0 ± 3.5</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>3.6 ± 0.7</t>
+          <t>9.7 ± 1.1</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>21.6 ± 1.9</t>
+          <t>42.1 ± 1.9</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>17.6 ± 1.2</t>
+          <t>24.9 ± 2.1</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -9554,32 +9554,32 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>17843.0 ± 50.1</t>
+          <t>30138.0 ± 207.4</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>10237.0 ± 28.5</t>
+          <t>17439.3 ± 140.2</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>43.8 ± 0.6</t>
+          <t>76.1 ± 3.5</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>3.8 ± 0.7</t>
+          <t>9.4 ± 1.1</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>21.6 ± 1.8</t>
+          <t>41.3 ± 1.9</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>17.2 ± 1.2</t>
+          <t>24.1 ± 2.2</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -9609,37 +9609,37 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>17630.8 ± 51.8</t>
+          <t>29827.6 ± 211.2</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>10109.6 ± 30.2</t>
+          <t>17256.3 ± 140.2</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>42.8 ± 1.2</t>
+          <t>75.7 ± 3.6</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>4.0 ± 0.9</t>
+          <t>9.3 ± 1.0</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>21.0 ± 1.9</t>
+          <t>40.9 ± 2.0</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>16.6 ± 0.9</t>
+          <t>24.1 ± 2.1</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>1.2 ± 0.3</t>
+          <t>1.4 ± 0.3</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -9664,32 +9664,32 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>17432.2 ± 53.0</t>
+          <t>29509.1 ± 209.9</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>9998.6 ± 33.5</t>
+          <t>17059.4 ± 141.0</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>42.4 ± 1.2</t>
+          <t>75.0 ± 3.4</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>4.0 ± 0.9</t>
+          <t>9.2 ± 1.0</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>20.6 ± 1.8</t>
+          <t>40.8 ± 1.8</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>16.6 ± 0.7</t>
+          <t>23.8 ± 2.1</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -9719,37 +9719,37 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>17269.4 ± 49.9</t>
+          <t>29190.3 ± 206.0</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>9897.4 ± 35.9</t>
+          <t>16869.7 ± 136.6</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>41.8 ± 1.5</t>
+          <t>73.0 ± 3.6</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>3.8 ± 0.7</t>
+          <t>8.8 ± 1.0</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>20.8 ± 1.8</t>
+          <t>39.6 ± 1.8</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>16.0 ± 0.6</t>
+          <t>23.3 ± 2.2</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>1.2 ± 0.3</t>
+          <t>1.2 ± 0.4</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -9774,37 +9774,37 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>17073.2 ± 50.6</t>
+          <t>28882.8 ± 202.6</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>9782.4 ± 36.3</t>
+          <t>16684.8 ± 133.4</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>42.2 ± 1.6</t>
+          <t>72.2 ± 3.4</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>3.6 ± 0.6</t>
+          <t>8.8 ± 1.0</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>21.4 ± 1.7</t>
+          <t>39.4 ± 1.6</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>16.0 ± 0.7</t>
+          <t>22.8 ± 2.3</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>1.2 ± 0.3</t>
+          <t>1.2 ± 0.4</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -9829,37 +9829,37 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>16871.2 ± 45.4</t>
+          <t>28577.4 ± 203.3</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>9660.2 ± 32.5</t>
+          <t>16501.2 ± 135.7</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>42.6 ± 1.9</t>
+          <t>71.0 ± 3.5</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>4.0 ± 0.7</t>
+          <t>8.5 ± 1.0</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>21.8 ± 1.7</t>
+          <t>38.8 ± 1.7</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>15.6 ± 0.9</t>
+          <t>22.4 ± 2.5</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>1.2 ± 0.3</t>
+          <t>1.2 ± 0.4</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -9884,37 +9884,37 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>16700.4 ± 49.7</t>
+          <t>28269.8 ± 200.5</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>9543.4 ± 37.5</t>
+          <t>16328.2 ± 135.0</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>40.6 ± 1.6</t>
+          <t>70.4 ± 3.5</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>3.6 ± 0.5</t>
+          <t>8.2 ± 1.1</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>21.2 ± 1.6</t>
+          <t>38.5 ± 1.8</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>14.4 ± 0.7</t>
+          <t>22.4 ± 2.3</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>1.4 ± 0.4</t>
+          <t>1.2 ± 0.4</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -9939,37 +9939,37 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>16508.4 ± 51.1</t>
+          <t>27969.5 ± 199.5</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>9435.8 ± 32.8</t>
+          <t>16143.8 ± 137.7</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>40.0 ± 1.3</t>
+          <t>69.6 ± 3.3</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>3.4 ± 0.4</t>
+          <t>8.2 ± 1.1</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>21.4 ± 1.4</t>
+          <t>38.0 ± 1.6</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>13.8 ± 1.0</t>
+          <t>22.2 ± 2.4</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>1.4 ± 0.4</t>
+          <t>1.2 ± 0.4</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -9994,37 +9994,37 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>16308.8 ± 48.7</t>
+          <t>27672.2 ± 203.2</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>9331.8 ± 31.2</t>
+          <t>15964.8 ± 138.6</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>40.6 ± 1.3</t>
+          <t>69.3 ± 3.5</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>3.4 ± 0.4</t>
+          <t>8.2 ± 1.1</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>21.8 ± 1.5</t>
+          <t>37.8 ± 1.7</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>14.0 ± 1.2</t>
+          <t>22.3 ± 2.4</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>1.4 ± 0.4</t>
+          <t>1.1 ± 0.4</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -10049,37 +10049,37 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>16133.0 ± 45.0</t>
+          <t>27360.0 ± 203.9</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>9242.4 ± 29.1</t>
+          <t>15780.9 ± 138.2</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>40.2 ± 1.5</t>
+          <t>68.7 ± 3.4</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>2.8 ± 0.5</t>
+          <t>8.0 ± 1.1</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>21.6 ± 1.6</t>
+          <t>37.8 ± 1.7</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>14.4 ± 1.3</t>
+          <t>21.8 ± 2.3</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>1.4 ± 0.4</t>
+          <t>1.1 ± 0.4</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -10104,37 +10104,37 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>15925.8 ± 48.9</t>
+          <t>27061.8 ± 204.7</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>9125.8 ± 30.9</t>
+          <t>15600.9 ± 136.8</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>41.0 ± 1.4</t>
+          <t>68.0 ± 3.4</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>2.8 ± 0.5</t>
+          <t>8.0 ± 1.1</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>22.8 ± 1.6</t>
+          <t>37.7 ± 1.6</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>14.0 ± 1.3</t>
+          <t>21.1 ± 2.3</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>1.4 ± 0.4</t>
+          <t>1.2 ± 0.4</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
